--- a/Codes/benchmark_winrates.xlsx
+++ b/Codes/benchmark_winrates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rgdar\OneDrive\Desktop\Academics\ASC\Final-Year-Project\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2D488B-63DB-4956-9ED7-E53F9D4E3D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6696575F-4C74-4BD6-B5F6-C4FFA296CB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Win Rates" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Algorithm</t>
   </si>
@@ -28,6 +28,12 @@
     <t>Run1</t>
   </si>
   <si>
+    <t>Run2</t>
+  </si>
+  <si>
+    <t>Run3</t>
+  </si>
+  <si>
     <t>CCE-TDCCEA</t>
   </si>
   <si>
@@ -58,7 +64,13 @@
     <t>SA-PDCoEA</t>
   </si>
   <si>
-    <t>Run2</t>
+    <t>Time1</t>
+  </si>
+  <si>
+    <t>Time2</t>
+  </si>
+  <si>
+    <t>Time3</t>
   </si>
 </sst>
 </file>
@@ -398,14 +410,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,117 +425,249 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>71.430000000000007</v>
       </c>
       <c r="C2">
+        <v>815.5</v>
+      </c>
+      <c r="D2">
         <v>91.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>85.71</v>
+      </c>
+      <c r="G2">
+        <v>915.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
       <c r="C3">
+        <v>869.7</v>
+      </c>
+      <c r="D3">
         <v>85.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>62.86</v>
+      </c>
+      <c r="G3">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>68.569999999999993</v>
       </c>
       <c r="C4">
+        <v>250.7</v>
+      </c>
+      <c r="D4">
         <v>62.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>14.29</v>
+      </c>
+      <c r="G4">
+        <v>135.80000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>80</v>
       </c>
       <c r="C5">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="D5">
         <v>42.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="G5">
+        <v>159.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>57.14</v>
       </c>
       <c r="C6">
+        <v>167.8</v>
+      </c>
+      <c r="D6">
         <v>31.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>165.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>14.29</v>
       </c>
       <c r="C7">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="D7">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>51.43</v>
+      </c>
+      <c r="G7">
+        <v>182.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>57.14</v>
       </c>
       <c r="C8">
+        <v>119.1</v>
+      </c>
+      <c r="D8">
         <v>71.400000000000006</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>45.71</v>
+      </c>
+      <c r="G8">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>85.71</v>
       </c>
       <c r="C9">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D9">
         <v>85.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>28.57</v>
+      </c>
+      <c r="G9">
+        <v>163.19999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>57.14</v>
       </c>
       <c r="C10">
+        <v>115.5</v>
+      </c>
+      <c r="D10">
         <v>51.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>57.14</v>
+      </c>
+      <c r="G10">
+        <v>137.80000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>85.71</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>71.400000000000006</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="G11">
+        <v>1885.8</v>
       </c>
     </row>
   </sheetData>

--- a/Codes/benchmark_winrates.xlsx
+++ b/Codes/benchmark_winrates.xlsx
@@ -1,94 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rgdar\OneDrive\Desktop\Academics\ASC\Final-Year-Project\Codes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6696575F-4C74-4BD6-B5F6-C4FFA296CB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Win Rates" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Win Rates" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Algorithm</t>
-  </si>
-  <si>
-    <t>Run1</t>
-  </si>
-  <si>
-    <t>Run2</t>
-  </si>
-  <si>
-    <t>Run3</t>
-  </si>
-  <si>
-    <t>CCE-TDCCEA</t>
-  </si>
-  <si>
-    <t>Standard CCEA</t>
-  </si>
-  <si>
-    <t>CMA-ES</t>
-  </si>
-  <si>
-    <t>DE/rand/1/bin</t>
-  </si>
-  <si>
-    <t>PSO</t>
-  </si>
-  <si>
-    <t>TD-CCEA</t>
-  </si>
-  <si>
-    <t>SA-TDCCEA</t>
-  </si>
-  <si>
-    <t>Hill Climbing</t>
-  </si>
-  <si>
-    <t>GESY</t>
-  </si>
-  <si>
-    <t>SA-PDCoEA</t>
-  </si>
-  <si>
-    <t>Time1</t>
-  </si>
-  <si>
-    <t>Time2</t>
-  </si>
-  <si>
-    <t>Time3</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -409,265 +407,443 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col width="13.109375" customWidth="1" min="1" max="1"/>
+    <col width="12.33203125" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>71.430000000000007</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Time1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Time2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Run3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Time3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Run5</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Time5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCE-TDCCEA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="C2" t="n">
         <v>815.5</v>
       </c>
-      <c r="D2">
-        <v>91.4</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>85.71</v>
-      </c>
-      <c r="G2">
+      <c r="D2" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G2" t="n">
         <v>915.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+      <c r="H2" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>380.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Standard CCEA</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>869.7</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>85.7</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>62.86</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>978</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>68.569999999999993</v>
-      </c>
-      <c r="C4">
+      <c r="H3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>417.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CMA-ES</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="C4" t="n">
         <v>250.7</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>62.9</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>14.29</v>
       </c>
-      <c r="G4">
-        <v>135.80000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+      <c r="G4" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="K4" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DE/rand/1/bin</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>80</v>
       </c>
-      <c r="C5">
-        <v>137.80000000000001</v>
-      </c>
-      <c r="D5">
+      <c r="C5" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="D5" t="n">
         <v>42.9</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>68.569999999999993</v>
-      </c>
-      <c r="G5">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="G5" t="n">
         <v>159.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
+      <c r="H5" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="I5" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>57.14</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>167.8</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>80</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>165.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
+      <c r="H6" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="I6" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TD-CCEA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>14.29</v>
       </c>
-      <c r="C7">
-        <v>159.30000000000001</v>
-      </c>
-      <c r="D7">
+      <c r="C7" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="D7" t="n">
         <v>14.3</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>51.43</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>182.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
+      <c r="H7" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SA-TDCCEA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>57.14</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>119.1</v>
       </c>
-      <c r="D8">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="D8" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>45.71</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>174.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>85.71</v>
-      </c>
-      <c r="C9">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="D9">
+      <c r="H8" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="K8" t="n">
+        <v>69.40000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hill Climbing</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="D9" t="n">
         <v>85.7</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>28.57</v>
       </c>
-      <c r="G9">
-        <v>163.19999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
+      <c r="G9" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="K9" t="n">
+        <v>71.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GESY</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>57.14</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>115.5</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>51.4</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>57.14</v>
       </c>
-      <c r="G10">
-        <v>137.80000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>85.71</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>71.430000000000007</v>
-      </c>
-      <c r="G11">
+      <c r="G10" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="I10" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="K10" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SA-PDCoEA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G11" t="n">
         <v>1885.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>857.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>745.9</v>
       </c>
     </row>
   </sheetData>

--- a/Codes/benchmark_winrates.xlsx
+++ b/Codes/benchmark_winrates.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.109375" customWidth="1" min="1" max="1"/>
@@ -475,6 +475,16 @@
           <t>Time5</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Run6</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Time6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -512,6 +522,12 @@
       <c r="K2" t="n">
         <v>380.9</v>
       </c>
+      <c r="L2" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>660.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +565,12 @@
       <c r="K3" t="n">
         <v>417.8</v>
       </c>
+      <c r="L3" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>410.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -586,6 +608,12 @@
       <c r="K4" t="n">
         <v>63.7</v>
       </c>
+      <c r="L4" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>76.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -623,6 +651,12 @@
       <c r="K5" t="n">
         <v>75</v>
       </c>
+      <c r="L5" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>73.59999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -660,6 +694,12 @@
       <c r="K6" t="n">
         <v>100.9</v>
       </c>
+      <c r="L6" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M6" t="n">
+        <v>71.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -697,6 +737,12 @@
       <c r="K7" t="n">
         <v>80</v>
       </c>
+      <c r="L7" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -734,6 +780,12 @@
       <c r="K8" t="n">
         <v>69.40000000000001</v>
       </c>
+      <c r="L8" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67.59999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -771,6 +823,12 @@
       <c r="K9" t="n">
         <v>71.7</v>
       </c>
+      <c r="L9" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>71.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -808,6 +866,12 @@
       <c r="K10" t="n">
         <v>61.5</v>
       </c>
+      <c r="L10" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -844,6 +908,12 @@
       </c>
       <c r="K11" t="n">
         <v>745.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>946.6</v>
       </c>
     </row>
   </sheetData>

--- a/Codes/benchmark_winrates.xlsx
+++ b/Codes/benchmark_winrates.xlsx
@@ -1,36 +1,133 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rgdar\OneDrive\Desktop\Academics\ASC\Final-Year-Project\Codes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4694663D-605E-47CA-A322-8FC012498D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Win Rates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Win Rates" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>Algorithm</t>
+  </si>
+  <si>
+    <t>Run1</t>
+  </si>
+  <si>
+    <t>Time1</t>
+  </si>
+  <si>
+    <t>Run2</t>
+  </si>
+  <si>
+    <t>Time2</t>
+  </si>
+  <si>
+    <t>Run3</t>
+  </si>
+  <si>
+    <t>Time3</t>
+  </si>
+  <si>
+    <t>Run4</t>
+  </si>
+  <si>
+    <t>Time4</t>
+  </si>
+  <si>
+    <t>Run5</t>
+  </si>
+  <si>
+    <t>Time5</t>
+  </si>
+  <si>
+    <t>Run6</t>
+  </si>
+  <si>
+    <t>Time6</t>
+  </si>
+  <si>
+    <t>CCE-TDCCEA</t>
+  </si>
+  <si>
+    <t>Standard CCEA</t>
+  </si>
+  <si>
+    <t>CMA-ES</t>
+  </si>
+  <si>
+    <t>DE/rand/1/bin</t>
+  </si>
+  <si>
+    <t>PSO</t>
+  </si>
+  <si>
+    <t>TD-CCEA</t>
+  </si>
+  <si>
+    <t>SA-TDCCEA</t>
+  </si>
+  <si>
+    <t>Hill Climbing</t>
+  </si>
+  <si>
+    <t>GESY</t>
+  </si>
+  <si>
+    <t>SA-PDCoEA</t>
+  </si>
+  <si>
+    <t>Run7</t>
+  </si>
+  <si>
+    <t>Time7</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,81 +142,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -407,513 +447,529 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="13.109375" customWidth="1" min="1" max="1"/>
-    <col width="12.33203125" customWidth="1" min="2" max="3"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Algorithm</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Time1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Run2</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Time2</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Run3</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Time3</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Run4</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Time4</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Run5</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Time5</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Run6</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Time6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CCE-TDCCEA</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="C2">
         <v>815.5</v>
       </c>
-      <c r="D2" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="D2">
+        <v>91.4</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>85.71</v>
+      </c>
+      <c r="G2">
         <v>915.3</v>
       </c>
-      <c r="H2" t="n">
-        <v>74.29000000000001</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="I2">
         <v>328.1</v>
       </c>
-      <c r="J2" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>85.71</v>
+      </c>
+      <c r="K2">
         <v>380.9</v>
       </c>
-      <c r="L2" t="n">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="L2">
+        <v>88.57</v>
+      </c>
+      <c r="M2">
         <v>660.1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Standard CCEA</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="N2">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="O2">
+        <v>902.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>100</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>869.7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>85.7</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>62.86</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>978</v>
       </c>
-      <c r="H3" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="I3">
         <v>313.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>37.14</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>417.8</v>
       </c>
-      <c r="L3" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3">
+        <v>85.71</v>
+      </c>
+      <c r="M3">
         <v>410.7</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CMA-ES</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>68.56999999999999</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="C4">
         <v>250.7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>62.9</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>14.29</v>
       </c>
-      <c r="G4" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="H4">
         <v>28.57</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>61.1</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>54.29</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>63.7</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>57.14</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>76.3</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DE/rand/1/bin</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="N4">
+        <v>28.57</v>
+      </c>
+      <c r="O4">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>80</v>
       </c>
-      <c r="C5" t="n">
-        <v>137.8</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="D5">
         <v>42.9</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68.56999999999999</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="G5">
         <v>159.1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>62.86</v>
       </c>
-      <c r="I5" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="I5">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="J5">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="K5">
         <v>75</v>
       </c>
-      <c r="L5" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>73.59999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PSO</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="L5">
+        <v>85.71</v>
+      </c>
+      <c r="M5">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="N5">
+        <v>74.290000000000006</v>
+      </c>
+      <c r="O5">
+        <v>133.80000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>57.14</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>167.8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>31.4</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>80</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>165.9</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>45.71</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>84.3</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>22.86</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>100.9</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>48.57</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>71.7</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TD-CCEA</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="N6">
+        <v>48.57</v>
+      </c>
+      <c r="O6">
+        <v>159.80000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>14.29</v>
       </c>
-      <c r="C7" t="n">
-        <v>159.3</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="D7">
         <v>14.3</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>51.43</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>182.5</v>
       </c>
-      <c r="H7" t="n">
-        <v>68.56999999999999</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="H7">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="I7">
         <v>62.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>22.86</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>80</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>37.14</v>
       </c>
-      <c r="M7" t="n">
-        <v>73.09999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SA-TDCCEA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="M7">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="N7">
+        <v>42.86</v>
+      </c>
+      <c r="O7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>57.14</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>119.1</v>
       </c>
-      <c r="D8" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="D8">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>45.71</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>174.5</v>
       </c>
-      <c r="H8" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="I8">
         <v>92.8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>28.57</v>
       </c>
-      <c r="K8" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K8">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="L8">
         <v>25.71</v>
       </c>
-      <c r="M8" t="n">
-        <v>67.59999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Hill Climbing</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="M8">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="N8">
+        <v>42.86</v>
+      </c>
+      <c r="O8">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>85.71</v>
+      </c>
+      <c r="C9">
+        <v>145.80000000000001</v>
+      </c>
+      <c r="D9">
         <v>85.7</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>28.57</v>
       </c>
-      <c r="G9" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G9">
+        <v>163.19999999999999</v>
+      </c>
+      <c r="H9">
+        <v>85.71</v>
+      </c>
+      <c r="I9">
         <v>51.6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>42.86</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>71.7</v>
       </c>
-      <c r="L9" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="L9">
+        <v>85.71</v>
+      </c>
+      <c r="M9">
         <v>71.5</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GESY</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="N9">
+        <v>48.57</v>
+      </c>
+      <c r="O9">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>57.14</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>115.5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>51.4</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>57.14</v>
       </c>
-      <c r="G10" t="n">
-        <v>137.8</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="H10">
         <v>31.43</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>51.2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>25.71</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>61.5</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>57.14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>64</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SA-PDCoEA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="N10">
+        <v>48.57</v>
+      </c>
+      <c r="O10">
+        <v>142.19999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>85.71</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="G11">
         <v>1885.8</v>
       </c>
-      <c r="H11" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="H11">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="I11">
         <v>857.9</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>77.14</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>745.9</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>51.43</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>946.6</v>
+      </c>
+      <c r="N11">
+        <v>57.14</v>
+      </c>
+      <c r="O11">
+        <v>1923.4</v>
       </c>
     </row>
   </sheetData>
